--- a/data/benchmark.xlsx
+++ b/data/benchmark.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22400" windowHeight="10080"/>
+    <workbookView windowHeight="16300"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="All" sheetId="1" r:id="rId1"/>
+    <sheet name="CNN" sheetId="4" r:id="rId2"/>
+    <sheet name="Transformer" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,95 +29,324 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="102">
   <si>
     <t>CAMO</t>
   </si>
   <si>
-    <t>CASIA</t>
-  </si>
-  <si>
-    <t>CHAMELEON</t>
-  </si>
-  <si>
     <t>COD10K</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
-    <t>GSD</t>
-  </si>
-  <si>
-    <t>ISTD</t>
-  </si>
-  <si>
-    <t>MSD</t>
-  </si>
-  <si>
     <t>NC4K</t>
   </si>
   <si>
-    <t>PMD</t>
-  </si>
-  <si>
-    <t>SBU</t>
-  </si>
-  <si>
-    <t>Trans10K</t>
+    <t>Methods</t>
+  </si>
+  <si>
+    <t>Pub./Year</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Backbone</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>WeightedFmeasure</t>
+  </si>
+  <si>
+    <t>Smeasure</t>
+  </si>
+  <si>
+    <t>Emeasure</t>
+  </si>
+  <si>
+    <t>CMeasure</t>
+  </si>
+  <si>
+    <t>SINet</t>
+  </si>
+  <si>
+    <t>CVPR 20</t>
+  </si>
+  <si>
+    <t>352 × 352</t>
+  </si>
+  <si>
+    <t>ResNet-50</t>
+  </si>
+  <si>
+    <t>PraNet</t>
+  </si>
+  <si>
+    <t>MICCAI 20</t>
+  </si>
+  <si>
+    <t>Res2Net-50</t>
+  </si>
+  <si>
+    <t>TINet</t>
+  </si>
+  <si>
+    <t>AAAI 21</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>CVPR 21</t>
+  </si>
+  <si>
+    <t>MGL-R</t>
+  </si>
+  <si>
+    <t>473 × 473</t>
+  </si>
+  <si>
+    <t>PFNet</t>
+  </si>
+  <si>
+    <t>416 × 416</t>
+  </si>
+  <si>
+    <t>UJSCOD</t>
+  </si>
+  <si>
+    <t>UGTR</t>
+  </si>
+  <si>
+    <t>ICCV 21</t>
+  </si>
+  <si>
+    <t>C2FNet</t>
+  </si>
+  <si>
+    <t>IJCAI 21</t>
+  </si>
+  <si>
+    <t>FDNet</t>
+  </si>
+  <si>
+    <t>CVPR 22</t>
+  </si>
+  <si>
+    <t>SegMaR</t>
+  </si>
+  <si>
+    <t>ZoomNet</t>
+  </si>
+  <si>
+    <t>384 × 384</t>
+  </si>
+  <si>
+    <t>BGNet</t>
+  </si>
+  <si>
+    <t>IJCAI 22</t>
+  </si>
+  <si>
+    <t>SINet-V2</t>
+  </si>
+  <si>
+    <t>TPAMI 22</t>
+  </si>
+  <si>
+    <t>TPRNet</t>
+  </si>
+  <si>
+    <t>TVCJ 22</t>
   </si>
   <si>
     <t>FEDER</t>
   </si>
   <si>
+    <t>CVPR 23</t>
+  </si>
+  <si>
+    <t>DGNet</t>
+  </si>
+  <si>
+    <t>MIR 23</t>
+  </si>
+  <si>
+    <t>EfficientNet-B4</t>
+  </si>
+  <si>
+    <t>DINet</t>
+  </si>
+  <si>
+    <t>TMM 24</t>
+  </si>
+  <si>
+    <t>400 × 400</t>
+  </si>
+  <si>
+    <t>RUN</t>
+  </si>
+  <si>
+    <t>ICML 25</t>
+  </si>
+  <si>
+    <t>DTINet</t>
+  </si>
+  <si>
+    <t>ICPR 22</t>
+  </si>
+  <si>
+    <t>256 × 256</t>
+  </si>
+  <si>
+    <t>ViT-B</t>
+  </si>
+  <si>
     <t>FSPNet</t>
   </si>
   <si>
-    <t>HetNet</t>
-  </si>
-  <si>
-    <t>HitNet</t>
-  </si>
-  <si>
-    <t>IML-ViT</t>
-  </si>
-  <si>
-    <t>ManTraNet</t>
-  </si>
-  <si>
-    <t>SAM_GTBBox</t>
-  </si>
-  <si>
-    <t>SAM2</t>
-  </si>
-  <si>
-    <t>SAM2_GTBBox</t>
-  </si>
-  <si>
-    <t>SegGPT</t>
-  </si>
-  <si>
-    <t>SINet</t>
-  </si>
-  <si>
-    <t>SINet-V2</t>
-  </si>
-  <si>
-    <t>UniverSeg</t>
-  </si>
-  <si>
-    <t>ZoomNet</t>
+    <t>RISNet</t>
+  </si>
+  <si>
+    <t>CVPR 24</t>
+  </si>
+  <si>
+    <t>704 × 704</t>
+  </si>
+  <si>
+    <t>PVTv2-B2</t>
+  </si>
+  <si>
+    <t>VSCode</t>
+  </si>
+  <si>
+    <t>Swin-S</t>
+  </si>
+  <si>
+    <t>FSEL</t>
+  </si>
+  <si>
+    <t>ECCV 24</t>
+  </si>
+  <si>
+    <t>PVTv2-B4</t>
+  </si>
+  <si>
+    <t>DPRNet</t>
+  </si>
+  <si>
+    <t>TCSVT 24</t>
+  </si>
+  <si>
+    <t>CamoFormer</t>
+  </si>
+  <si>
+    <t>TPAMI 24</t>
+  </si>
+  <si>
+    <t>ZoomNeXt</t>
+  </si>
+  <si>
+    <t>ESCNet</t>
+  </si>
+  <si>
+    <t>ICCV 25</t>
+  </si>
+  <si>
+    <t>PVTv2-B5</t>
+  </si>
+  <si>
+    <t>SAM-TTT</t>
+  </si>
+  <si>
+    <t>MM 25</t>
+  </si>
+  <si>
+    <t>1024 × 1024</t>
+  </si>
+  <si>
+    <t>SAM ViT-B</t>
+  </si>
+  <si>
+    <t>CFRN</t>
+  </si>
+  <si>
+    <t>TIP 25</t>
+  </si>
+  <si>
+    <t>Swin-B</t>
+  </si>
+  <si>
+    <t>SENet</t>
+  </si>
+  <si>
+    <t>CODIB</t>
+  </si>
+  <si>
+    <t>TMM 25</t>
+  </si>
+  <si>
+    <t>SFCNet</t>
+  </si>
+  <si>
+    <t>SMT-T</t>
+  </si>
+  <si>
+    <t>UTNet</t>
+  </si>
+  <si>
+    <t>Camodiffusion</t>
+  </si>
+  <si>
+    <t>TPAMI 25</t>
+  </si>
+  <si>
+    <t>VSCode-V2</t>
+  </si>
+  <si>
+    <t>GBNet</t>
+  </si>
+  <si>
+    <t>TIP 26</t>
+  </si>
+  <si>
+    <t>ICL-Camo</t>
+  </si>
+  <si>
+    <t>392 × 392</t>
+  </si>
+  <si>
+    <t>SAM2-UNet</t>
+  </si>
+  <si>
+    <t>VINT 26</t>
+  </si>
+  <si>
+    <t>SAM2-Hiera-L</t>
+  </si>
+  <si>
+    <t>DepthSAM</t>
+  </si>
+  <si>
+    <t>CVPR 26</t>
+  </si>
+  <si>
+    <t>512 × 512</t>
+  </si>
+  <si>
+    <t>DAv2 ViT-L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -575,159 +806,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1255,623 +1490,5014 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:S42"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="14" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.0865384615385" style="2" customWidth="1"/>
+    <col min="4" max="6" width="10.6346153846154" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.2692307692308" style="2" customWidth="1"/>
+    <col min="8" max="18" width="10.6346153846154" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.54807692307692" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="16.25" customHeight="1" spans="2:15">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="O1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="I2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.7616</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.4828</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.8444</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.7356</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.1636</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.8616</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.9289</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.8545</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.7953</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.74</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0.8593</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0.9475</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.099657</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.605563</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.751457</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.834471</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.650249</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.051128</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.550906</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.771005</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0.797101</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.617628</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.057642</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.722733</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.807991</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0.883296</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0.740042</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.094187</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.662526</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.769226</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.834652</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.70668</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.045115</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.629389</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.789443</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.839695</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.684459</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.058789</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.724494</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.822175</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.875388</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0.760371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.086519</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.67822</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.780525</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.846748</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.723309</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.042487</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.635046</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.793153</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.847513</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.683746</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.055159</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.733748</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.82872</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0.881908</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0.761201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.080103</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.696298</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.787163</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.859164</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.721905</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.036757</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0.672823</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0.804423</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0.882844</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.702821</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.048011</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.765542</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.839503</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0.904087</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0.77644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.088399</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.672794</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.7755</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.847619</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.699782</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.035307</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.665533</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.813968</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.863801</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.697354</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.052593</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.739183</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.832596</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0.889353</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0.757284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.084899</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.695206</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.782256</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.854705</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.72308</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.039606</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.65987</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0.799842</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.86827</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.699616</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.052748</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.745268</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.82904</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0.893747</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0.766045</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.072976</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.727947</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.800146</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.872263</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.748471</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.035309</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0.683755</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0.808883</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0.882195</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0.712549</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.046549</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.771283</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.841519</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0.906175</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0.781794</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.085855</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.686196</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.784734</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.860968</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.718708</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.035389</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.666958</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.817769</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0.849922</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0.704865</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.051778</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.746907</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.839349</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0.888733</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0.770079</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.079885</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.718651</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.796138</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.864866</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.743556</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.036024</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.68619</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.812951</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0.88559</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0.72223</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.049049</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.762383</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.838344</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0.901005</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0.784486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.06291</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.774585</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.841511</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.901407</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.807508</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.029717</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.728842</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.840418</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.905786</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.76756</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.051732</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0.749598</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.833874</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.895454</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0.778682</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.070936</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.752903</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.815499</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.88136</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.771215</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.033879</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.724022</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.833103</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.893434</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.745458</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.04582</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.78104</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.840568</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.905253</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.779395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.065936</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.752241</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.819749</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.8825</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.772882</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.028911</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0.72875</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0.838408</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0.892921</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0.742305</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.043368</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.784401</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.852816</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0.906819</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0.791568</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.073405</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.748517</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.811574</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.876195</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.769641</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.032558</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0.721886</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0.830679</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0.902128</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0.74488</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.04439</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.788375</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.851026</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0.910757</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0.798772</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.070489</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.742566</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.820105</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.884171</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.777817</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.036773</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0.67962</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0.815121</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0.86355</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0.725571</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0.047611</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0.769817</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0.847236</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0.901089</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0.793961</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.073811</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.725481</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.807198</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.880208</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.755895</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.036002</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.683469</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.817006</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.869252</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.720905</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.047575</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.768127</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.846428</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.901153</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.786477</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.071223</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.73773</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.8021</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.876645</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.760299</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.0316</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0.715542</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0.822312</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0.901024</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0.736154</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.044251</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.788638</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0.847044</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0.912969</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0.794146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.057195</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.76882</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.839056</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.906121</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.800454</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.033057</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0.692961</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0.822305</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0.878622</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.736336</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0.042465</v>
+      </c>
+      <c r="P19" s="4">
+        <v>0.783666</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0.856899</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0.910366</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0.805161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.068195</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.747675</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.821122</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.883726</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.777683</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.031368</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0.723548</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0.832042</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0.901534</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0.750047</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0.043484</v>
+      </c>
+      <c r="P20" s="4">
+        <v>0.790312</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0.855821</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0.912295</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0.804858</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.068671</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.744457</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.8126</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.883647</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.771912</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.029101</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0.735249</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0.839059</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0.909856</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0.766572</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0.042466</v>
+      </c>
+      <c r="P21" s="4">
+        <v>0.790033</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0.854142</v>
+      </c>
+      <c r="R21" s="4">
+        <v>0.915765</v>
+      </c>
+      <c r="S21" s="4">
+        <v>0.808133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.050383</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.795635</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.856</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.917904</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.828566</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.034223</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.694648</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0.823918</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0.880803</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0.737303</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0.040644</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0.792326</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0.86274</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0.914331</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0.81572</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.050307</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0.79893</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0.855948</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.919147</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.819795</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.026374</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0.734659</v>
+      </c>
+      <c r="L23" s="4">
+        <v>0.850643</v>
+      </c>
+      <c r="M23" s="4">
+        <v>0.899883</v>
+      </c>
+      <c r="N23" s="4">
+        <v>0.761906</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0.034984</v>
+      </c>
+      <c r="P23" s="4">
+        <v>0.815595</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>0.878501</v>
+      </c>
+      <c r="R23" s="4">
+        <v>0.923001</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0.827113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.050426</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0.827368</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0.869549</v>
+      </c>
+      <c r="H24" s="4">
+        <v>0.921756</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0.847184</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.024702</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0.798985</v>
+      </c>
+      <c r="L24" s="4">
+        <v>0.87335</v>
+      </c>
+      <c r="M24" s="4">
+        <v>0.927288</v>
+      </c>
+      <c r="N24" s="4">
+        <v>0.806292</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0.036649</v>
+      </c>
+      <c r="P24" s="4">
+        <v>0.834196</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>0.881713</v>
+      </c>
+      <c r="R24" s="4">
+        <v>0.926387</v>
+      </c>
+      <c r="S24" s="4">
+        <v>0.83697</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.046051</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0.820375</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.873297</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0.928323</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.843096</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.023476</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.780379</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0.86878</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0.928707</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.79582</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0.031537</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0.84127</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0.891029</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0.938631</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0.845411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.040004</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.850789</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0.884853</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.942449</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0.866938</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.021145</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.799578</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0.876536</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0.927702</v>
+      </c>
+      <c r="N26" s="4">
+        <v>0.814974</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0.029895</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0.852937</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0.892991</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0.940829</v>
+      </c>
+      <c r="S26" s="4">
+        <v>0.854939</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.045998</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0.829911</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0.864964</v>
+      </c>
+      <c r="H27" s="4">
+        <v>0.93098</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0.844797</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0.024945</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0.771456</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0.854432</v>
+      </c>
+      <c r="M27" s="4">
+        <v>0.925979</v>
+      </c>
+      <c r="N27" s="4">
+        <v>0.788372</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0.03275</v>
+      </c>
+      <c r="P27" s="4">
+        <v>0.838395</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>0.879573</v>
+      </c>
+      <c r="R27" s="4">
+        <v>0.936511</v>
+      </c>
+      <c r="S27" s="4">
+        <v>0.839721</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.046098</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0.830599</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0.871779</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0.931051</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0.848221</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0.022559</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0.78638</v>
+      </c>
+      <c r="L28" s="4">
+        <v>0.869074</v>
+      </c>
+      <c r="M28" s="4">
+        <v>0.930989</v>
+      </c>
+      <c r="N28" s="4">
+        <v>0.800612</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0.030128</v>
+      </c>
+      <c r="P28" s="4">
+        <v>0.847008</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>0.891535</v>
+      </c>
+      <c r="R28" s="4">
+        <v>0.940926</v>
+      </c>
+      <c r="S28" s="4">
+        <v>0.849856</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.040405</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0.859478</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0.888091</v>
+      </c>
+      <c r="H29" s="4">
+        <v>0.935113</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0.868392</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0.016973</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0.838263</v>
+      </c>
+      <c r="L29" s="4">
+        <v>0.898277</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0.945402</v>
+      </c>
+      <c r="N29" s="4">
+        <v>0.835778</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0.027706</v>
+      </c>
+      <c r="P29" s="4">
+        <v>0.865329</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>0.900448</v>
+      </c>
+      <c r="R29" s="4">
+        <v>0.943264</v>
+      </c>
+      <c r="S29" s="4">
+        <v>0.860059</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.040774</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0.84883</v>
+      </c>
+      <c r="G30" s="4">
+        <v>0.875478</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.940346</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.858211</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.020412</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0.808231</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0.873488</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0.944463</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0.812948</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0.027838</v>
+      </c>
+      <c r="P30" s="4">
+        <v>0.863953</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0.892857</v>
+      </c>
+      <c r="R30" s="4">
+        <v>0.948664</v>
+      </c>
+      <c r="S30" s="4">
+        <v>0.857771</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.045524</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0.837374</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0.868514</v>
+      </c>
+      <c r="H31" s="4">
+        <v>0.942049</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.854931</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.024241</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0.801214</v>
+      </c>
+      <c r="L31" s="4">
+        <v>0.873989</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0.931562</v>
+      </c>
+      <c r="N31" s="4">
+        <v>0.819002</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0.032814</v>
+      </c>
+      <c r="P31" s="4">
+        <v>0.854315</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0.890245</v>
+      </c>
+      <c r="R31" s="4">
+        <v>0.946195</v>
+      </c>
+      <c r="S31" s="4">
+        <v>0.856707</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.03901</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0.848512</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.880843</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0.943075</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.863766</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0.020854</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0.799517</v>
+      </c>
+      <c r="L32" s="4">
+        <v>0.872395</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0.939453</v>
+      </c>
+      <c r="N32" s="4">
+        <v>0.812053</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0.029101</v>
+      </c>
+      <c r="P32" s="4">
+        <v>0.854557</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0.89105</v>
+      </c>
+      <c r="R32" s="4">
+        <v>0.947337</v>
+      </c>
+      <c r="S32" s="4">
+        <v>0.855662</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.03877</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0.847013</v>
+      </c>
+      <c r="G33" s="4">
+        <v>0.888407</v>
+      </c>
+      <c r="H33" s="4">
+        <v>0.926797</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0.864406</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.023902</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0.779063</v>
+      </c>
+      <c r="L33" s="4">
+        <v>0.865339</v>
+      </c>
+      <c r="M33" s="4">
+        <v>0.919181</v>
+      </c>
+      <c r="N33" s="4">
+        <v>0.794531</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0.031921</v>
+      </c>
+      <c r="P33" s="4">
+        <v>0.843483</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>0.888758</v>
+      </c>
+      <c r="R33" s="4">
+        <v>0.930212</v>
+      </c>
+      <c r="S33" s="4">
+        <v>0.844688</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.044982</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0.831155</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0.875448</v>
+      </c>
+      <c r="H34" s="4">
+        <v>0.923765</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0.849559</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.02277</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0.787417</v>
+      </c>
+      <c r="L34" s="4">
+        <v>0.869709</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0.9261</v>
+      </c>
+      <c r="N34" s="4">
+        <v>0.80221</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0.031793</v>
+      </c>
+      <c r="P34" s="4">
+        <v>0.844778</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>0.89004</v>
+      </c>
+      <c r="R34" s="4">
+        <v>0.931825</v>
+      </c>
+      <c r="S34" s="4">
+        <v>0.847487</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.042251</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0.84561</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0.881545</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0.934342</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.86045</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0.021773</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0.797447</v>
+      </c>
+      <c r="L35" s="4">
+        <v>0.872347</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.93825</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0.804539</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0.030883</v>
+      </c>
+      <c r="P35" s="4">
+        <v>0.849591</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0.890649</v>
+      </c>
+      <c r="R35" s="4">
+        <v>0.939427</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0.847204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.048858</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0.82867</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0.867855</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0.925667</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0.84539</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0.022398</v>
+      </c>
+      <c r="K36" s="4">
+        <v>0.791345</v>
+      </c>
+      <c r="L36" s="4">
+        <v>0.868223</v>
+      </c>
+      <c r="M36" s="4">
+        <v>0.933167</v>
+      </c>
+      <c r="N36" s="4">
+        <v>0.799023</v>
+      </c>
+      <c r="O36" s="3">
+        <v>0.032036</v>
+      </c>
+      <c r="P36" s="4">
+        <v>0.845693</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0.88743</v>
+      </c>
+      <c r="R36" s="4">
+        <v>0.938114</v>
+      </c>
+      <c r="S36" s="4">
+        <v>0.844815</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.042376</v>
+      </c>
+      <c r="F37" s="4">
+        <v>0.85125</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0.878121</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0.939945</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0.859958</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0.019005</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0.81682</v>
+      </c>
+      <c r="L37" s="4">
+        <v>0.883029</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0.946286</v>
+      </c>
+      <c r="N37" s="4">
+        <v>0.817885</v>
+      </c>
+      <c r="O37" s="3">
+        <v>0.028323</v>
+      </c>
+      <c r="P37" s="4">
+        <v>0.860894</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>0.895103</v>
+      </c>
+      <c r="R37" s="4">
+        <v>0.945948</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0.854027</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.048603</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.817204</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0.874944</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0.921482</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0.840361</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0.023694</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0.786984</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0.874049</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0.925344</v>
+      </c>
+      <c r="N38" s="4">
+        <v>0.80073</v>
+      </c>
+      <c r="O38" s="3">
+        <v>0.031195</v>
+      </c>
+      <c r="P38" s="3">
+        <v>0.845395</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>0.896533</v>
+      </c>
+      <c r="R38" s="3">
+        <v>0.937574</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0.848596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0.044</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0.847414</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0.880945</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0.926423</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0.862471</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0.019008</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0.837026</v>
+      </c>
+      <c r="L39" s="4">
+        <v>0.897669</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0.944955</v>
+      </c>
+      <c r="N39" s="4">
+        <v>0.838313</v>
+      </c>
+      <c r="O39" s="3">
+        <v>0.030385</v>
+      </c>
+      <c r="P39" s="4">
+        <v>0.859814</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>0.897484</v>
+      </c>
+      <c r="R39" s="4">
+        <v>0.934711</v>
+      </c>
+      <c r="S39" s="4">
+        <v>0.858333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.036927</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0.858965</v>
+      </c>
+      <c r="G40" s="4">
+        <v>0.892119</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0.94429</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.870252</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0.016613</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0.834191</v>
+      </c>
+      <c r="L40" s="4">
+        <v>0.896363</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.949806</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0.837471</v>
+      </c>
+      <c r="O40" s="3">
+        <v>0.023791</v>
+      </c>
+      <c r="P40" s="4">
+        <v>0.878994</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0.912032</v>
+      </c>
+      <c r="R40" s="4">
+        <v>0.954449</v>
+      </c>
+      <c r="S40" s="4">
+        <v>0.872806</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.042122</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0.844699</v>
+      </c>
+      <c r="G41" s="4">
+        <v>0.883629</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0.933421</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0.858507</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0.020992</v>
+      </c>
+      <c r="K41" s="4">
+        <v>0.798311</v>
+      </c>
+      <c r="L41" s="4">
+        <v>0.880311</v>
+      </c>
+      <c r="M41" s="4">
+        <v>0.926162</v>
+      </c>
+      <c r="N41" s="4">
+        <v>0.812951</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0.02935</v>
+      </c>
+      <c r="P41" s="4">
+        <v>0.856329</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>0.901009</v>
+      </c>
+      <c r="R41" s="4">
+        <v>0.940328</v>
+      </c>
+      <c r="S41" s="4">
+        <v>0.856809</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.028033</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0.894839</v>
+      </c>
+      <c r="G42" s="4">
+        <v>0.919015</v>
+      </c>
+      <c r="H42" s="4">
+        <v>0.960236</v>
+      </c>
+      <c r="I42" s="4">
+        <v>0.898304</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0.014279</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0.871626</v>
+      </c>
+      <c r="L42" s="4">
+        <v>0.919867</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0.960465</v>
+      </c>
+      <c r="N42" s="4">
+        <v>0.86378</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0.020758</v>
+      </c>
+      <c r="P42" s="4">
+        <v>0.902275</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>0.928926</v>
+      </c>
+      <c r="R42" s="4">
+        <v>0.961887</v>
+      </c>
+      <c r="S42" s="4">
+        <v>0.889515</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="O1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S21"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.099657</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.605563</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.751457</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.834471</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.650249</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.051128</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.550906</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.771005</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0.797101</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.617628</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.057642</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.722733</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.807991</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0.883296</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0.740042</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.094187</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.662526</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.769226</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.834652</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.70668</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.045115</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.629389</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.789443</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.839695</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.684459</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.058789</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.724494</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.822175</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.875388</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0.760371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.086519</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.67822</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.780525</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.846748</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.723309</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.042487</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.635046</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.793153</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.847513</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.683746</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.055159</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.733748</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.82872</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0.881908</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0.761201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.080103</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.696298</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.787163</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.859164</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.721905</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.036757</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0.672823</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0.804423</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0.882844</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.702821</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.048011</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.765542</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.839503</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0.904087</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0.77644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.088399</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.672794</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.7755</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.847619</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.699782</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.035307</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.665533</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.813968</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.863801</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.697354</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.052593</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.739183</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.832596</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0.889353</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0.757284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.084899</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.695206</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.782256</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.854705</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.72308</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.039606</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.65987</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0.799842</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.86827</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.699616</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.052748</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.745268</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.82904</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0.893747</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0.766045</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.072976</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.727947</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.800146</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.872263</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.748471</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.035309</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0.683755</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0.808883</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0.882195</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0.712549</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.046549</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.771283</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.841519</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0.906175</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0.781794</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.085855</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.686196</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.784734</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.860968</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.718708</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.035389</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.666958</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.817769</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0.849922</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0.704865</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.051778</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.746907</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.839349</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0.888733</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0.770079</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.079885</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.718651</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.796138</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.864866</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.743556</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.036024</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.68619</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.812951</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0.88559</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0.72223</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.049049</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.762383</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.838344</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0.901005</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0.784486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.06291</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.774585</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.841511</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.901407</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.807508</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.029717</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.728842</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.840418</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.905786</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.76756</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.051732</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0.749598</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.833874</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.895454</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0.778682</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.070936</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.752903</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.815499</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.88136</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.771215</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.033879</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.724022</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.833103</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.893434</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.745458</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.04582</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.78104</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.840568</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.905253</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.779395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.065936</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.752241</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.819749</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.8825</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.772882</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.028911</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0.72875</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0.838408</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0.892921</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0.742305</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.043368</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.784401</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.852816</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0.906819</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0.791568</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.073405</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.748517</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.811574</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.876195</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.769641</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.032558</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0.721886</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0.830679</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0.902128</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0.74488</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.04439</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.788375</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.851026</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0.910757</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0.798772</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.070489</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.742566</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.820105</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.884171</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.777817</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.036773</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0.67962</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0.815121</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0.86355</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0.725571</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0.047611</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0.769817</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0.847236</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0.901089</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0.793961</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.073811</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.725481</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.807198</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.880208</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.755895</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.036002</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.683469</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0.817006</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0.869252</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.720905</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.047575</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.768127</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.846428</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.901153</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.786477</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.071223</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.73773</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.8021</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.876645</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.760299</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.0316</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0.715542</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0.822312</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0.901024</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0.736154</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.044251</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.788638</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0.847044</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0.912969</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0.794146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.057195</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.76882</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.839056</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.906121</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.800454</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.033057</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0.692961</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0.822305</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0.878622</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.736336</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0.042465</v>
+      </c>
+      <c r="P19" s="4">
+        <v>0.783666</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0.856899</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0.910366</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0.805161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.068195</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.747675</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.821122</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.883726</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.777683</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.031368</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0.723548</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0.832042</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0.901534</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0.750047</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0.043484</v>
+      </c>
+      <c r="P20" s="4">
+        <v>0.790312</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0.855821</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0.912295</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0.804858</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.068671</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.744457</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.8126</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.883647</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.771912</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.029101</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0.735249</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0.839059</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0.909856</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0.766572</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0.042466</v>
+      </c>
+      <c r="P21" s="4">
+        <v>0.790033</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0.854142</v>
+      </c>
+      <c r="R21" s="4">
+        <v>0.915765</v>
+      </c>
+      <c r="S21" s="4">
+        <v>0.808133</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="O1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1" spans="5:19">
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.816</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.6597</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.8533</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.7566</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.2771</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.8809</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.8837</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.8926</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.8249</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.7441</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0.8641</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0.9483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.050383</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.795635</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.856</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.917904</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.828566</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.034223</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.694648</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.823918</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.880803</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.737303</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.040644</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0.792326</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.86274</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0.914331</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0.81572</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.050307</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.79893</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.855948</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.919147</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.819795</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.026374</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.734659</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.850643</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.899883</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.761906</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.034984</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.815595</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.878501</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.923001</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0.827113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.050426</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.827368</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.869549</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.921756</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.847184</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.024702</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.798985</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.87335</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.927288</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.806292</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.036649</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.834196</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.881713</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0.926387</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0.83697</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.7606</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.4602</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.8471</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.7293</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.1066</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.8666</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.9055</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.8547</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.8012</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.749</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0.8539</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0.9477</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.686</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.4606</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.7198</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.6846</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.1313</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.8556</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.9217</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.7662</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.7609</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.5049</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0.8335</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0.7899</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.7274</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.6192</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.7033</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.7402</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.2334</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.8747</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.9009</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.8254</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.7955</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0.6807</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0.8484</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0.695</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.3493</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.1573</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.304</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.2163</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.1757</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.5498</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.7235</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.3372</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.3193</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.1776</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0.698</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.6133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.8643</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.8203</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.8385</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.8442</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.8617</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.879</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.7894</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.7522</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.8667</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0.843</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0.7425</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0.8978</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.6433</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.3401</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.6395</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.6491</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.3897</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.227</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0.3811</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.2496</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.731</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0.1219</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0.3155</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0.4598</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.8795</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.8329</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.8804</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.8813</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.8622</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.876</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0.7842</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.7634</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.8984</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0.8292</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0.7524</v>
-      </c>
-      <c r="M10" s="2">
-        <v>0.9207</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.3115</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.0388</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.3859</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.3733</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.0323</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.2872</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0.1299</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.1594</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.4124</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0.2638</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0.066</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0.2764</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.634</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.4282</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.7233</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.5656</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.1428</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.8373</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0.8615</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.8044</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.6771</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0.6809</v>
-      </c>
-      <c r="L12" s="2">
-        <v>0.8126</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0.7778</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.7772</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.5571</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.8393</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.7167</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.2084</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.8697</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0.9227</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.8237</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0.7878</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0.7643</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0.8602</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0.8313</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.2834</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.1657</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.2293</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.165</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.2238</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.3236</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0.1621</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0.2705</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0.2531</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0.1443</v>
-      </c>
-      <c r="L14" s="2">
-        <v>0.172</v>
-      </c>
-      <c r="M14" s="2">
-        <v>0.3306</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0.7217</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0.4331</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.8136</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.7089</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.1742</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.8434</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0.855</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0.7644</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0.7714</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0.6979</v>
-      </c>
-      <c r="L15" s="2">
-        <v>0.8452</v>
-      </c>
-      <c r="M15" s="2">
-        <v>0.9366</v>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.046051</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.820375</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.873297</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.928323</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.843096</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.023476</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.780379</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.86878</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.928707</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.79582</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.031537</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0.84127</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.891029</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0.938631</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0.845411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.040004</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.850789</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.884853</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.942449</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.866938</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.021145</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.799578</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.876536</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.927702</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0.814974</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.029895</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.852937</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.892991</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0.940829</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0.854939</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.045998</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.829911</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.864964</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.93098</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.844797</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.024945</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.771456</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0.854432</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.925979</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.788372</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.03275</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.838395</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.879573</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0.936511</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0.839721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.046098</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.830599</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.871779</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.931051</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.848221</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.022559</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0.78638</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0.869074</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0.930989</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0.800612</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.030128</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.847008</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.891535</v>
+      </c>
+      <c r="R9" s="4">
+        <v>0.940926</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0.849856</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.040405</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.859478</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.888091</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.935113</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.868392</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.016973</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.838263</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.898277</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0.945402</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0.835778</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.027706</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.865329</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.900448</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0.943264</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0.860059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.040774</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.84883</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.875478</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.940346</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.858211</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.020412</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.808231</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.873488</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0.944463</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0.812948</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.027838</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.863953</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.892857</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0.948664</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0.857771</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.045524</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.837374</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.868514</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.942049</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.854931</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.024241</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0.801214</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0.873989</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0.931562</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0.819002</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.032814</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.854315</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.890245</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0.946195</v>
+      </c>
+      <c r="S12" s="4">
+        <v>0.856707</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.03901</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.848512</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.880843</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.943075</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.863766</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.020854</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0.799517</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0.872395</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0.939453</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0.812053</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.029101</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.854557</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.89105</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0.947337</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0.855662</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.03877</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.847013</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.888407</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.926797</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.864406</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.023902</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0.779063</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0.865339</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0.919181</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0.794531</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.031921</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.843483</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.888758</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0.930212</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0.844688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.044982</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.831155</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.875448</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.923765</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.849559</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.02277</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0.787417</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0.869709</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0.9261</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0.80221</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.031793</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.844778</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.89004</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0.931825</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0.847487</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.042251</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.84561</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.881545</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.934342</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.86045</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.021773</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0.797447</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0.872347</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0.93825</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0.804539</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0.030883</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0.849591</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0.890649</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0.939427</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0.847204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.048858</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.82867</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.867855</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.925667</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.84539</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.022398</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0.791345</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0.868223</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0.933167</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0.799023</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.032036</v>
+      </c>
+      <c r="P17" s="4">
+        <v>0.845693</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>0.88743</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0.938114</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0.844815</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.042376</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.85125</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.878121</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.939945</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.859958</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.019005</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0.81682</v>
+      </c>
+      <c r="L18" s="4">
+        <v>0.883029</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0.946286</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0.817885</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.028323</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0.860894</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>0.895103</v>
+      </c>
+      <c r="R18" s="4">
+        <v>0.945948</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0.854027</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.048603</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.817204</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.874944</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.921482</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.840361</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.023694</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.786984</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.874049</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0.925344</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.80073</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0.031195</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0.845395</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0.896533</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0.937574</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0.848596</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.044</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.847414</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.880945</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.926423</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.862471</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.019008</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0.837026</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0.897669</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0.944955</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0.838313</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0.030385</v>
+      </c>
+      <c r="P20" s="4">
+        <v>0.859814</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0.897484</v>
+      </c>
+      <c r="R20" s="4">
+        <v>0.934711</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0.858333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.036927</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.858965</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.892119</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.94429</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.870252</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.016613</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0.834191</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0.896363</v>
+      </c>
+      <c r="M21" s="4">
+        <v>0.949806</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0.837471</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0.023791</v>
+      </c>
+      <c r="P21" s="4">
+        <v>0.878994</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>0.912032</v>
+      </c>
+      <c r="R21" s="4">
+        <v>0.954449</v>
+      </c>
+      <c r="S21" s="4">
+        <v>0.872806</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.042122</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.844699</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0.883629</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.933421</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.858507</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.020992</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0.798311</v>
+      </c>
+      <c r="L22" s="4">
+        <v>0.880311</v>
+      </c>
+      <c r="M22" s="4">
+        <v>0.926162</v>
+      </c>
+      <c r="N22" s="4">
+        <v>0.812951</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0.02935</v>
+      </c>
+      <c r="P22" s="4">
+        <v>0.856329</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>0.901009</v>
+      </c>
+      <c r="R22" s="4">
+        <v>0.940328</v>
+      </c>
+      <c r="S22" s="4">
+        <v>0.856809</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.028033</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0.894839</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0.919015</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.960236</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.898304</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.014279</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0.871626</v>
+      </c>
+      <c r="L23" s="4">
+        <v>0.919867</v>
+      </c>
+      <c r="M23" s="4">
+        <v>0.960465</v>
+      </c>
+      <c r="N23" s="4">
+        <v>0.86378</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0.020758</v>
+      </c>
+      <c r="P23" s="4">
+        <v>0.902275</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>0.928926</v>
+      </c>
+      <c r="R23" s="4">
+        <v>0.961887</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0.889515</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="O1:S1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
